--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260730.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260730.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>28.56%</t>
+          <t>28.76%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>7.87%</t>
+          <t>8.26%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.58%</t>
+          <t>6.85%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.03%</t>
+          <t>5.76%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.65%</t>
+          <t>5.01%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.87%</t>
+          <t>3.54%</t>
         </is>
       </c>
     </row>
@@ -748,51 +748,51 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.54%</t>
+          <t>3.34%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>DUK US</t>
+          <t>EQIX US</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>杜克能源公司</t>
+          <t>Equinix公司</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>50,435</t>
+          <t>6,325</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.29%</t>
+          <t>3.22%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>EQIX US</t>
+          <t>DUK US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Equinix公司</t>
+          <t>杜克能源公司</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>6,325</t>
+          <t>50,435</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.22%</t>
+          <t>3.09%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.87%</t>
+          <t>2.82%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>2.80%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.18%</t>
         </is>
       </c>
     </row>
@@ -880,178 +880,178 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>2.12%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>D US</t>
+          <t>HPE US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>道明尼能源公司</t>
+          <t>慧與</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>56,845</t>
+          <t>85,365</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>1.95%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>HPE US</t>
+          <t>D US</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>慧與</t>
+          <t>道明尼能源公司</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>85,365</t>
+          <t>56,845</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.93%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>29,548</t>
+          <t>21,690</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.57%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>XEL US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Xcel 能源</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>40,290</t>
+          <t>29,548</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.55%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>EXC US</t>
+          <t>XEL US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>愛克斯龍公司</t>
+          <t>Xcel 能源</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>66,058</t>
+          <t>40,290</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.53%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>EXC US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>愛克斯龍公司</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>21,690</t>
+          <t>66,058</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.56%</t>
+          <t>1.46%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>23,698</t>
+          <t>8,790</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.28%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>141,205</t>
+          <t>23,698</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,176 +1063,176 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>20,515</t>
+          <t>141,205</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.22%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>8,790</t>
+          <t>12,951</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>66,944,471</t>
+          <t>20,515</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>17,671</t>
+          <t>10,566</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>12,951</t>
+          <t>66,944,471</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>C_USD</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>10,566</t>
+          <t>1,984,130</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>41,880</t>
+          <t>17,671</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>PPL Corp</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>48,100</t>
+          <t>41,880</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
@@ -1254,29 +1254,29 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>C_USD</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>PPL Corp</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>1,514,827</t>
+          <t>48,100</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
@@ -1319,28 +1319,6 @@
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>RDI_USD</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>466,876</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>0.00%</t>
         </is>
